--- a/output/pdf_financials_xlsx/IPO.xlsx
+++ b/output/pdf_financials_xlsx/IPO.xlsx
@@ -431,6 +431,21 @@
   </sheetPr>
   <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/IPO.xlsx
+++ b/output/pdf_financials_xlsx/IPO.xlsx
@@ -1135,7 +1135,7 @@
         <v>-17.924</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>20.019</v>
+        <v>-20.019</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-7.701</v>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>91.107</v>
+        <v>-139.035</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>12.269</v>
+        <v>-6.669</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-5.416</v>
@@ -1371,7 +1371,7 @@
         <v>-17.924</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>20.019</v>
+        <v>-20.019</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-7.701</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>115.071</v>
+        <v>-115.071</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>9.468999999999999</v>
+        <v>-9.468999999999999</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-7.842</v>
@@ -1522,7 +1522,7 @@
         <v>-17.924</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>20.019</v>
+        <v>-20.019</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-7.701</v>
@@ -1537,7 +1537,7 @@
         <v>-112.629</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>115.071</v>
+        <v>-115.071</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>9.468999999999999</v>
+        <v>-9.468999999999999</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-7.842</v>
@@ -1770,7 +1770,7 @@
         <v>-18.045</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>20.019</v>
+        <v>-20.019</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-7.701</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>91.127</v>
+        <v>-139.015</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>13.56</v>
+        <v>-5.378</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-4.418</v>
@@ -1872,7 +1872,7 @@
         <v>-1.129</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>33.744</v>
+        <v>-6.294</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>14.85</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>118.567</v>
+        <v>-111.575</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>61.769</v>
+        <v>42.831</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>93.634</v>
@@ -1927,7 +1927,7 @@
         <v>-3.817800622210199</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>132.9446064139942</v>
+        <v>-24.79710030730439</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>26.53112270420925</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>115.9477405411749</v>
+        <v>-109.1102005691431</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46.18277519831924</v>
+        <v>32.02341699751026</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>37.18231780926362</v>
@@ -1980,7 +1980,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>26.30313806842504</v>
+        <v>-17.23594778293236</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>22.82174586355856</v>
+        <v>-41.98530514319988</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-44.79320531757755</v>
@@ -2035,7 +2035,7 @@
         <v>-60.61138915190044</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>78.87085336064928</v>
+        <v>-78.87085336064928</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>-13.75866504680912</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>112.528970555159</v>
+        <v>-112.528970555159</v>
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>7.079679100404489</v>
+        <v>-7.079679100404489</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>-3.114079674693436</v>
@@ -5036,7 +5036,7 @@
         <v>-17.924</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>20.019</v>
+        <v>-20.019</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-7.701</v>
@@ -5051,7 +5051,7 @@
         <v>-112.629</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>115.071</v>
+        <v>-115.071</v>
       </c>
       <c r="J99" s="1" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>9.468999999999999</v>
+        <v>-9.468999999999999</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-7.842</v>
@@ -5956,12 +5956,10 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.636</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>7.034</v>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
@@ -15194,7 +15192,7 @@
         </is>
       </c>
       <c r="O113" s="5" t="n">
-        <v>9.468999999999999</v>
+        <v>-9.468999999999999</v>
       </c>
       <c r="P113" s="5" t="n">
         <v>-7.842</v>
@@ -19381,7 +19379,7 @@
         <v>-112.629</v>
       </c>
       <c r="L172" s="5" t="n">
-        <v>115.071</v>
+        <v>-115.071</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -20500,7 +20498,11 @@
           <t>Exploration and evaluation expense 8</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -21506,7 +21508,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>20.019</v>
+        <v>-20.019</v>
       </c>
       <c r="H201" s="5" t="n">
         <v>-7.701</v>

--- a/output/pdf_financials_xlsx/IPO.xlsx
+++ b/output/pdf_financials_xlsx/IPO.xlsx
@@ -6273,30 +6273,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G124" s="3" t="n">
+        <v>-0.284</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>-0.599</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.476</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.347</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.424</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-1.802</v>
       </c>
     </row>
     <row r="125">
@@ -6322,30 +6318,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G125" s="3" t="n">
+        <v>-0.284</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>-0.599</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.476</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.347</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.424</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-1.802</v>
       </c>
     </row>
     <row r="126">
@@ -15870,7 +15862,11 @@
           <t>Principal portion of finance lease payments 9</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -17650,7 +17646,11 @@
           <t>Principal portion of finance lease payments 8</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -19566,7 +19566,11 @@
           <t>Principal portion of finance lease payments 9 $</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -26192,7 +26196,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -27756,7 +27760,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -29246,7 +29250,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">

--- a/output/pdf_financials_xlsx/IPO.xlsx
+++ b/output/pdf_financials_xlsx/IPO.xlsx
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>20.648</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>20.72</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-56.655</v>
+        <v>-77.303</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-18.045</v>
+        <v>-38.765</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-20.019</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-30.672</v>
+        <v>-51.32</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.129</v>
+        <v>-21.849</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-6.294</v>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-3.817800622210199</v>
+        <v>-73.88407953469498</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-24.79710030730439</v>
@@ -35826,7 +35826,11 @@
           <t>Net finance expenses</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E392" s="5" t="n">
         <v>-10.324</v>
       </c>
@@ -37250,7 +37254,11 @@
           <t>Net finance expenses $</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E411" s="5" t="n">
         <v>-10.324</v>
       </c>
